--- a/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/consolidado_provisiones.xlsx
+++ b/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/consolidado_provisiones.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J234"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3592,24 +3592,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="E67" t="n">
-        <v>3179094.59</v>
+        <v>4495658.38</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3640,24 +3640,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Corporativo</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="E68" t="n">
-        <v>4867271.77</v>
+        <v>1719177.73</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3666,17 +3666,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3688,24 +3688,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="E69" t="n">
-        <v>3238990.02</v>
+        <v>150797.41</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3736,12 +3736,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Corporativo</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3753,7 +3753,7 @@
         <v>6310</v>
       </c>
       <c r="E70" t="n">
-        <v>4668141.86</v>
+        <v>3686952.43</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3767,12 +3767,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3784,24 +3784,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="E71" t="n">
-        <v>830742.04</v>
+        <v>1870644.49</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3810,17 +3810,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3832,12 +3832,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Corporativo</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3849,7 +3849,7 @@
         <v>6310</v>
       </c>
       <c r="E72" t="n">
-        <v>836992.37</v>
+        <v>575688.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Ricardo Torres</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3880,24 +3880,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Corporativo</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="E73" t="n">
-        <v>4438598.26</v>
+        <v>2608771.37</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3906,17 +3906,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3928,12 +3928,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3945,7 +3945,7 @@
         <v>6310</v>
       </c>
       <c r="E74" t="n">
-        <v>4948908.83</v>
+        <v>123426.37</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3954,17 +3954,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3976,24 +3976,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Corporativo</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="E75" t="n">
-        <v>4944211.77</v>
+        <v>4391275.16</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4024,12 +4024,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4041,7 +4041,7 @@
         <v>6310</v>
       </c>
       <c r="E76" t="n">
-        <v>245542.83</v>
+        <v>9787663.59</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>cumplimiento.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4072,24 +4072,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E77" t="n">
-        <v>620461.9300000001</v>
+        <v>320037.98</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4120,24 +4120,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6410</v>
+        <v>6310</v>
       </c>
       <c r="E78" t="n">
-        <v>369153.2</v>
+        <v>4580940.72</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4146,17 +4146,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4168,24 +4168,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6410</v>
+        <v>6310</v>
       </c>
       <c r="E79" t="n">
-        <v>2545001.25</v>
+        <v>522759.47</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4194,17 +4194,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4216,24 +4216,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E80" t="n">
-        <v>2852720.38</v>
+        <v>2920875.5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4242,17 +4242,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4264,24 +4264,24 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6410</v>
+        <v>6310</v>
       </c>
       <c r="E81" t="n">
-        <v>4474759.56</v>
+        <v>3700069.04</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4295,12 +4295,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4312,24 +4312,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E82" t="n">
-        <v>4576150.7</v>
+        <v>2470151.46</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4338,17 +4338,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4360,24 +4360,24 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E83" t="n">
-        <v>3877714.2</v>
+        <v>2008510.13</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4408,24 +4408,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E84" t="n">
-        <v>1757706.56</v>
+        <v>1312803.06</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4456,24 +4456,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6410</v>
+        <v>6310</v>
       </c>
       <c r="E85" t="n">
-        <v>4563887.32</v>
+        <v>288000.68</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4482,17 +4482,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4504,24 +4504,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6410</v>
+        <v>6310</v>
       </c>
       <c r="E86" t="n">
-        <v>384239.73</v>
+        <v>1974060.3</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4530,17 +4530,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4552,24 +4552,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E87" t="n">
-        <v>2402448.98</v>
+        <v>1545132.81</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4578,17 +4578,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Andrés García</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4600,24 +4600,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6410</v>
+        <v>6310</v>
       </c>
       <c r="E88" t="n">
-        <v>936573.21</v>
+        <v>1278983.61</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4626,17 +4626,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4648,24 +4648,24 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E89" t="n">
-        <v>745881.3</v>
+        <v>3031823.55</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4696,24 +4696,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E90" t="n">
-        <v>2419534.67</v>
+        <v>16809829.15</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4744,24 +4744,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6410</v>
+        <v>6310</v>
       </c>
       <c r="E91" t="n">
-        <v>3205318.48</v>
+        <v>4943950</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>inversiones.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4792,24 +4792,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E92" t="n">
-        <v>2316767.16</v>
+        <v>759994.1899999999</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4818,17 +4818,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4840,7 +4840,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4857,7 +4857,7 @@
         <v>6310</v>
       </c>
       <c r="E93" t="n">
-        <v>784985.49</v>
+        <v>469172.2</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4871,12 +4871,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4888,24 +4888,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6410</v>
+        <v>6210</v>
       </c>
       <c r="E94" t="n">
-        <v>376219.98</v>
+        <v>3225462.46</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4936,12 +4936,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4953,7 +4953,7 @@
         <v>6310</v>
       </c>
       <c r="E95" t="n">
-        <v>4682279.42</v>
+        <v>225168.46</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4984,24 +4984,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6110</v>
+        <v>6310</v>
       </c>
       <c r="E96" t="n">
-        <v>407063.34</v>
+        <v>2374264.72</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5010,17 +5010,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5032,25 +5032,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E97" t="n">
-        <v>2349617.61</v>
-      </c>
+        <v>6210</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>Provisión</t>
@@ -5058,17 +5056,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5080,24 +5078,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>6120</v>
+        <v>6210</v>
       </c>
       <c r="E98" t="n">
-        <v>4252918.15</v>
+        <v>4202386.07</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5106,17 +5104,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>seguros.xlsx</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5128,24 +5126,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6310</v>
+        <v>6120</v>
       </c>
       <c r="E99" t="n">
-        <v>1272849.56</v>
+        <v>105019.16</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5164,7 +5162,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5176,24 +5174,24 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>6410</v>
+        <v>6110</v>
       </c>
       <c r="E100" t="n">
-        <v>2112082.52</v>
+        <v>85510.42999999999</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5202,17 +5200,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5224,24 +5222,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6310</v>
+        <v>6120</v>
       </c>
       <c r="E101" t="n">
-        <v>4895259.05</v>
+        <v>635716.41</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -5250,17 +5248,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5272,7 +5270,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5282,14 +5280,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>6410</v>
+        <v>6110</v>
       </c>
       <c r="E102" t="n">
-        <v>3931579.47</v>
+        <v>640262.73</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -5298,17 +5296,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5320,7 +5318,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5337,7 +5335,7 @@
         <v>6120</v>
       </c>
       <c r="E103" t="n">
-        <v>2966044.91</v>
+        <v>2546089.22</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5346,17 +5344,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5368,24 +5366,24 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6110</v>
+        <v>6120</v>
       </c>
       <c r="E104" t="n">
-        <v>161309.27</v>
+        <v>2188351.62</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -5399,12 +5397,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5416,12 +5414,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5433,7 +5431,7 @@
         <v>6110</v>
       </c>
       <c r="E105" t="n">
-        <v>2490769.93</v>
+        <v>944009.12</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5447,12 +5445,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5464,12 +5462,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5481,7 +5479,7 @@
         <v>6120</v>
       </c>
       <c r="E106" t="n">
-        <v>3474694.42</v>
+        <v>3344621.29</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5490,17 +5488,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5512,24 +5510,24 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6110</v>
+        <v>6120</v>
       </c>
       <c r="E107" t="n">
-        <v>2817882.69</v>
+        <v>2361894.02</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5538,17 +5536,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5560,24 +5558,24 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6410</v>
+        <v>6110</v>
       </c>
       <c r="E108" t="n">
-        <v>4241708.83</v>
+        <v>306201.98</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5586,17 +5584,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5608,7 +5606,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5618,14 +5616,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6410</v>
+        <v>6120</v>
       </c>
       <c r="E109" t="n">
-        <v>3440854.78</v>
+        <v>4742172.64</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5634,17 +5632,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5656,7 +5654,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5673,7 +5671,7 @@
         <v>6120</v>
       </c>
       <c r="E110" t="n">
-        <v>2878653.32</v>
+        <v>3468195.79</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5682,17 +5680,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5704,12 +5702,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5721,7 +5719,7 @@
         <v>6110</v>
       </c>
       <c r="E111" t="n">
-        <v>3320589.48</v>
+        <v>723942.34</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5735,12 +5733,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Daniela Vargas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5752,12 +5750,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5769,7 +5767,7 @@
         <v>6110</v>
       </c>
       <c r="E112" t="n">
-        <v>1341417.97</v>
+        <v>2416192.03</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5783,12 +5781,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5800,7 +5798,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5810,14 +5808,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6310</v>
+        <v>6120</v>
       </c>
       <c r="E113" t="n">
-        <v>1750932.38</v>
+        <v>2664254.38</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5826,17 +5824,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5848,24 +5846,24 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6410</v>
+        <v>6120</v>
       </c>
       <c r="E114" t="n">
-        <v>3494322.49</v>
+        <v>4177849.49</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5874,17 +5872,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5901,7 +5899,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5913,7 +5911,7 @@
         <v>6120</v>
       </c>
       <c r="E115" t="n">
-        <v>3078278.54</v>
+        <v>184371.11</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5927,12 +5925,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5944,7 +5942,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5954,14 +5952,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6310</v>
+        <v>6120</v>
       </c>
       <c r="E116" t="n">
-        <v>382967.04</v>
+        <v>1723581.61</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5970,17 +5968,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -5992,12 +5990,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6009,7 +6007,7 @@
         <v>6120</v>
       </c>
       <c r="E117" t="n">
-        <v>16822601.53</v>
+        <v>4082062.54</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6018,17 +6016,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6040,24 +6038,24 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6410</v>
+        <v>6110</v>
       </c>
       <c r="E118" t="n">
-        <v>2527657.08</v>
+        <v>2170309.8</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6066,17 +6064,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6088,24 +6086,24 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6310</v>
+        <v>6120</v>
       </c>
       <c r="E119" t="n">
-        <v>4819488.88</v>
+        <v>4908715.09</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -6114,17 +6112,17 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6136,24 +6134,24 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6310</v>
+        <v>6120</v>
       </c>
       <c r="E120" t="n">
-        <v>3413267.11</v>
+        <v>841058.13</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -6162,17 +6160,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6184,24 +6182,24 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6410</v>
+        <v>6120</v>
       </c>
       <c r="E121" t="n">
-        <v>3534354.58</v>
+        <v>4632070.91</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -6210,17 +6208,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Carlos Mendoza</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6232,7 +6230,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6242,14 +6240,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>6410</v>
+        <v>6120</v>
       </c>
       <c r="E122" t="n">
-        <v>2235768.27</v>
+        <v>14180711.93</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -6258,17 +6256,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6280,7 +6278,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6290,14 +6288,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6310</v>
+        <v>6120</v>
       </c>
       <c r="E123" t="n">
-        <v>2331196.89</v>
+        <v>3749175.92</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -6311,12 +6309,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Andrés García</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6328,24 +6326,24 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6410</v>
+        <v>6110</v>
       </c>
       <c r="E124" t="n">
-        <v>4350550.47</v>
+        <v>4860731.28</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -6354,17 +6352,17 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6376,7 +6374,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6386,14 +6384,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>6120</v>
+        <v>6110</v>
       </c>
       <c r="E125" t="n">
-        <v>797598.8100000001</v>
+        <v>1364383.94</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -6402,17 +6400,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6424,24 +6422,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6310</v>
+        <v>6110</v>
       </c>
       <c r="E126" t="n">
-        <v>4368782.6</v>
+        <v>541879.02</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -6450,17 +6448,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6472,7 +6470,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6482,14 +6480,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6410</v>
+        <v>6120</v>
       </c>
       <c r="E127" t="n">
-        <v>4430499.91</v>
+        <v>1709912.06</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -6498,17 +6496,17 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sofía Hernández</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6520,7 +6518,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6530,14 +6528,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>6410</v>
+        <v>6120</v>
       </c>
       <c r="E128" t="n">
-        <v>4959255.12</v>
+        <v>3794328.64</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -6546,17 +6544,17 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tarjetas.xlsx</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6568,24 +6566,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6310</v>
+        <v>6410</v>
       </c>
       <c r="E129" t="n">
-        <v>988034.83</v>
+        <v>1221262.44</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -6599,12 +6597,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6616,12 +6614,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6633,7 +6631,7 @@
         <v>6410</v>
       </c>
       <c r="E130" t="n">
-        <v>1928714.47</v>
+        <v>4342289.75</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6642,17 +6640,17 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6664,12 +6662,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6681,7 +6679,7 @@
         <v>6410</v>
       </c>
       <c r="E131" t="n">
-        <v>3329383.89</v>
+        <v>1376521.16</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6690,17 +6688,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Daniela Vargas</t>
+          <t>Ricardo Torres</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -6712,24 +6710,24 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6120</v>
+        <v>6410</v>
       </c>
       <c r="E132" t="n">
-        <v>1967948.72</v>
+        <v>2925873.46</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -6738,17 +6736,17 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6760,24 +6758,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6110</v>
+        <v>6410</v>
       </c>
       <c r="E133" t="n">
-        <v>2915595.12</v>
+        <v>1727373.62</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6786,17 +6784,17 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Patricia Díaz</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6808,24 +6806,24 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6310</v>
+        <v>6410</v>
       </c>
       <c r="E134" t="n">
-        <v>4332862.5</v>
+        <v>544355.61</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6839,12 +6837,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Patricia Díaz</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -6856,24 +6854,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6120</v>
+        <v>6410</v>
       </c>
       <c r="E135" t="n">
-        <v>1824629.87</v>
+        <v>1930890.76</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6882,17 +6880,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -6904,24 +6902,24 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6310</v>
+        <v>6410</v>
       </c>
       <c r="E136" t="n">
-        <v>1634098.24</v>
+        <v>160862.65</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6930,17 +6928,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Ana López</t>
+          <t>Carlos Mendoza</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6952,24 +6950,24 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6110</v>
+        <v>6410</v>
       </c>
       <c r="E137" t="n">
-        <v>1859708.35</v>
+        <v>300922.17</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6978,17 +6976,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Miguel Ruiz</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7000,24 +6998,24 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6110</v>
+        <v>6410</v>
       </c>
       <c r="E138" t="n">
-        <v>2699307.76</v>
+        <v>3401524.32</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -7026,17 +7024,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Sofía Hernández</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7048,24 +7046,24 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6120</v>
+        <v>6410</v>
       </c>
       <c r="E139" t="n">
-        <v>4947806.35</v>
+        <v>263054.29</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -7074,17 +7072,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Laura Castillo</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7096,12 +7094,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7113,7 +7111,7 @@
         <v>6410</v>
       </c>
       <c r="E140" t="n">
-        <v>1574653.84</v>
+        <v>2867446.19</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -7122,17 +7120,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Ana López</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7144,24 +7142,24 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6110</v>
+        <v>6410</v>
       </c>
       <c r="E141" t="n">
-        <v>3494360.86</v>
+        <v>2941787.97</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -7170,7 +7168,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7180,7 +7178,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7192,24 +7190,24 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6120</v>
+        <v>6410</v>
       </c>
       <c r="E142" t="n">
-        <v>1644031.09</v>
+        <v>50590.97</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -7218,17 +7216,17 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Fernanda Reyes</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7240,24 +7238,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6110</v>
+        <v>6410</v>
       </c>
       <c r="E143" t="n">
-        <v>1546382.08</v>
+        <v>3390733.87</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -7266,17 +7264,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Laura Castillo</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7288,12 +7286,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7305,7 +7303,7 @@
         <v>6410</v>
       </c>
       <c r="E144" t="n">
-        <v>2120192.52</v>
+        <v>1216936.03</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -7319,12 +7317,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>María Sánchez</t>
+          <t>Fernanda Reyes</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7336,12 +7334,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7353,7 +7351,7 @@
         <v>6410</v>
       </c>
       <c r="E145" t="n">
-        <v>1997665.34</v>
+        <v>4111681.72</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -7367,12 +7365,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Miguel Ruiz</t>
+          <t>Javier Morales</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -7384,24 +7382,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>6120</v>
+        <v>6410</v>
       </c>
       <c r="E146" t="n">
-        <v>4263035.94</v>
+        <v>1309916.84</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -7410,7 +7408,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7420,4232 +7418,10 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>riesgos.xlsx</t>
+          <t>tesoreria.xlsx</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Banca Corporativa</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E147" t="n">
-        <v>4511649.78</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>riesgos.xlsx</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Banca Corporativa</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E148" t="n">
-        <v>3321436.24</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Ana López</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>riesgos.xlsx</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E149" t="n">
-        <v>476875.4</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Andrés García</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>riesgos.xlsx</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Banca Comercial</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E150" t="n">
-        <v>4437233.62</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>riesgos.xlsx</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Banca Comercial</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E151" t="n">
-        <v>3828000.9</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>riesgos.xlsx</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Banca Comercial</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E152" t="n">
-        <v>715817.6800000001</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>riesgos.xlsx</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Inversiones</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E153" t="n">
-        <v>3633620.7</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>riesgos.xlsx</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Inversiones</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E154" t="n">
-        <v>328582.42</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>riesgos.xlsx</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E155" t="n">
-        <v>4495658.38</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Patricia Díaz</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E156" t="n">
-        <v>1719177.73</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Daniela Vargas</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E157" t="n">
-        <v>150797.41</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Daniela Vargas</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E158" t="n">
-        <v>3686952.43</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E159" t="n">
-        <v>1870644.49</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Daniela Vargas</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E160" t="n">
-        <v>575688.2</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Ana López</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E161" t="n">
-        <v>2608771.37</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E162" t="n">
-        <v>123426.37</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E163" t="n">
-        <v>4391275.16</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Andrés García</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E164" t="n">
-        <v>9787663.59</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E165" t="n">
-        <v>320037.98</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>María Sánchez</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E166" t="n">
-        <v>4580940.72</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E167" t="n">
-        <v>522759.47</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E168" t="n">
-        <v>2920875.5</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E169" t="n">
-        <v>3700069.04</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Patricia Díaz</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E170" t="n">
-        <v>2470151.46</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Andrés García</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E171" t="n">
-        <v>2008510.13</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Patricia Díaz</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E172" t="n">
-        <v>1312803.06</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E173" t="n">
-        <v>288000.68</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E174" t="n">
-        <v>1974060.3</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E175" t="n">
-        <v>1545132.81</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Andrés García</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E176" t="n">
-        <v>1278983.61</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Daniela Vargas</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>2026-01-17</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E177" t="n">
-        <v>3031823.55</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Daniela Vargas</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E178" t="n">
-        <v>16809829.15</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E179" t="n">
-        <v>4943950</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E180" t="n">
-        <v>759994.1899999999</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E181" t="n">
-        <v>469172.2</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E182" t="n">
-        <v>3225462.46</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Andrés García</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E183" t="n">
-        <v>225168.46</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>6310</v>
-      </c>
-      <c r="E184" t="n">
-        <v>2374264.72</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>6210</v>
-      </c>
-      <c r="E186" t="n">
-        <v>4202386.07</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>María Sánchez</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>seguros.xlsx</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E187" t="n">
-        <v>105019.16</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E188" t="n">
-        <v>85510.42999999999</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E189" t="n">
-        <v>635716.41</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E190" t="n">
-        <v>640262.73</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E191" t="n">
-        <v>2546089.22</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E192" t="n">
-        <v>2188351.62</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E193" t="n">
-        <v>944009.12</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E194" t="n">
-        <v>3344621.29</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E195" t="n">
-        <v>2361894.02</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E196" t="n">
-        <v>306201.98</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E197" t="n">
-        <v>4742172.64</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E198" t="n">
-        <v>3468195.79</v>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E199" t="n">
-        <v>723942.34</v>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Daniela Vargas</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E200" t="n">
-        <v>2416192.03</v>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E201" t="n">
-        <v>2664254.38</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E202" t="n">
-        <v>4177849.49</v>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E203" t="n">
-        <v>184371.11</v>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>María Sánchez</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E204" t="n">
-        <v>1723581.61</v>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E205" t="n">
-        <v>4082062.54</v>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E206" t="n">
-        <v>2170309.8</v>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Ana López</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E207" t="n">
-        <v>4908715.09</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E208" t="n">
-        <v>841058.13</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>María Sánchez</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E209" t="n">
-        <v>4632070.91</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E210" t="n">
-        <v>14180711.93</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E211" t="n">
-        <v>3749175.92</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E212" t="n">
-        <v>4860731.28</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E213" t="n">
-        <v>1364383.94</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E214" t="n">
-        <v>541879.02</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E215" t="n">
-        <v>1709912.06</v>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>6120</v>
-      </c>
-      <c r="E216" t="n">
-        <v>3794328.64</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>tarjetas.xlsx</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E217" t="n">
-        <v>1221262.44</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E218" t="n">
-        <v>4342289.75</v>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E219" t="n">
-        <v>1376521.16</v>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Ricardo Torres</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E220" t="n">
-        <v>2925873.46</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Patricia Díaz</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E221" t="n">
-        <v>1727373.62</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E222" t="n">
-        <v>544355.61</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Patricia Díaz</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E223" t="n">
-        <v>1930890.76</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>María Sánchez</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E224" t="n">
-        <v>160862.65</v>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Carlos Mendoza</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E225" t="n">
-        <v>300922.17</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Miguel Ruiz</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E226" t="n">
-        <v>3401524.32</v>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sofía Hernández</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E227" t="n">
-        <v>263054.29</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Laura Castillo</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E228" t="n">
-        <v>2867446.19</v>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Ana López</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E229" t="n">
-        <v>2941787.97</v>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Ana López</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E230" t="n">
-        <v>50590.97</v>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E231" t="n">
-        <v>3390733.87</v>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E232" t="n">
-        <v>1216936.03</v>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Fernanda Reyes</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E233" t="n">
-        <v>4111681.72</v>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Javier Morales</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E234" t="n">
-        <v>1309916.84</v>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>Provisión</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Ana López</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>tesoreria.xlsx</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
         <is>
           <t>Provisión</t>
         </is>
@@ -11662,7 +7438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11699,10 +7475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>98236437.92</v>
+        <v>78802530.18000001</v>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -11717,52 +7493,47 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72682449</v>
+        <v>66040151.96</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Banca Corporativa</t>
+          <t>Seguros</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pérdida esperada</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55538723.95</v>
+        <v>53843330.9</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reserva técnica seguros</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53843330.9</v>
+        <v>34531099.79</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11771,34 +7542,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48340993.16</v>
+        <v>34084023.82</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>Banca Comercial</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Provisión regulatoria</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42472228.72</v>
+        <v>32820734.72</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Banca Comercial</t>
+          <t>Banca Corporativa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11807,262 +7578,47 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36354435.09</v>
+        <v>29672361.75</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Banca Corporativa</t>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Reserva crediticia</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35483721.16</v>
+        <v>25058724.37</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Corporativo</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ajuste de valuación</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>34084023.82</v>
+        <v>14053422.67</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>21314724.71</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>19755216.03</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>17954846.87</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Banca Corporativa</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>17295188.32</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Banca Comercial</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>10827016.22</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>10818560.49</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Inversiones</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>10809975.44</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>10523720.55</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Banca Corporativa</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>9965065.48</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Tarjetas</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>7704086.33</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Inversiones</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4661444.92</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Banca Comercial</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2304934.45</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A17:A18"/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
